--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,22 +11654,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11813,22 +11813,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17547,12 +17547,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G108" t="n">

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,22 +11495,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,22 +11654,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="O78" t="n">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="P78" t="n">
-        <v>3.31</v>
+        <v>3.69</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="O79" t="n">
-        <v>3.54</v>
+        <v>3.33</v>
       </c>
       <c r="P79" t="n">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G106" t="n">

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU108"/>
+  <dimension ref="A1:AU107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7356,12 +7356,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7506,7 +7506,7 @@
         <v>0</v>
       </c>
       <c r="AU44" s="3" t="n">
-        <v>46172.4375</v>
+        <v>46172.45833333334</v>
       </c>
     </row>
     <row r="45">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8310,27 +8310,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8460,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="AU50" s="3" t="n">
-        <v>46172.45833333334</v>
+        <v>46172.46875</v>
       </c>
     </row>
     <row r="51">
@@ -8469,27 +8469,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="AU51" s="3" t="n">
-        <v>46172.46875</v>
+        <v>46172.5</v>
       </c>
     </row>
     <row r="52">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8989,17 +8989,17 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9096,7 +9096,7 @@
         <v>0</v>
       </c>
       <c r="AU54" s="3" t="n">
-        <v>46172.5</v>
+        <v>46172.54166666666</v>
       </c>
     </row>
     <row r="55">
@@ -9105,27 +9105,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9255,7 +9255,7 @@
         <v>0</v>
       </c>
       <c r="AU55" s="3" t="n">
-        <v>46172.54166666666</v>
+        <v>46172.5625</v>
       </c>
     </row>
     <row r="56">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9414,7 +9414,7 @@
         <v>0</v>
       </c>
       <c r="AU56" s="3" t="n">
-        <v>46172.5625</v>
+        <v>46172.60416666666</v>
       </c>
     </row>
     <row r="57">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9573,7 +9573,7 @@
         <v>0</v>
       </c>
       <c r="AU57" s="3" t="n">
-        <v>46172.60416666666</v>
+        <v>46172.625</v>
       </c>
     </row>
     <row r="58">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10209,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="AU61" s="3" t="n">
-        <v>46172.625</v>
+        <v>46172.64583333334</v>
       </c>
     </row>
     <row r="62">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10686,7 +10686,7 @@
         <v>0</v>
       </c>
       <c r="AU64" s="3" t="n">
-        <v>46172.64583333334</v>
+        <v>46172.66666666666</v>
       </c>
     </row>
     <row r="65">
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,22 +11495,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,22 +11654,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12126,12 +12126,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12276,7 +12276,7 @@
         <v>0</v>
       </c>
       <c r="AU74" s="3" t="n">
-        <v>46172.66666666666</v>
+        <v>46172.70833333334</v>
       </c>
     </row>
     <row r="75">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12603,12 +12603,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12753,7 +12753,7 @@
         <v>0</v>
       </c>
       <c r="AU77" s="3" t="n">
-        <v>46172.70833333334</v>
+        <v>46172.72916666666</v>
       </c>
     </row>
     <row r="78">
@@ -12921,12 +12921,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>0</v>
       </c>
       <c r="AU79" s="3" t="n">
-        <v>46172.72916666666</v>
+        <v>46172.75</v>
       </c>
     </row>
     <row r="80">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13398,12 +13398,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13548,7 +13548,7 @@
         <v>0</v>
       </c>
       <c r="AU82" s="3" t="n">
-        <v>46172.75</v>
+        <v>46172.76041666666</v>
       </c>
     </row>
     <row r="83">
@@ -13557,12 +13557,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13707,7 +13707,7 @@
         <v>0</v>
       </c>
       <c r="AU83" s="3" t="n">
-        <v>46172.76041666666</v>
+        <v>46172.77083333334</v>
       </c>
     </row>
     <row r="84">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -14034,12 +14034,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="AU86" s="3" t="n">
-        <v>46172.77083333334</v>
+        <v>46172.79166666666</v>
       </c>
     </row>
     <row r="87">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14511,12 +14511,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14661,7 +14661,7 @@
         <v>0</v>
       </c>
       <c r="AU89" s="3" t="n">
-        <v>46172.79166666666</v>
+        <v>46172.8125</v>
       </c>
     </row>
     <row r="90">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14829,12 +14829,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14979,7 +14979,7 @@
         <v>0</v>
       </c>
       <c r="AU91" s="3" t="n">
-        <v>46172.8125</v>
+        <v>46172.83333333334</v>
       </c>
     </row>
     <row r="92">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15624,12 +15624,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15774,7 +15774,7 @@
         <v>0</v>
       </c>
       <c r="AU96" s="3" t="n">
-        <v>46172.83333333334</v>
+        <v>46172.85416666666</v>
       </c>
     </row>
     <row r="97">
@@ -15783,12 +15783,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15933,7 +15933,7 @@
         <v>0</v>
       </c>
       <c r="AU97" s="3" t="n">
-        <v>46172.85416666666</v>
+        <v>46172.875</v>
       </c>
     </row>
     <row r="98">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16887,7 +16887,7 @@
         <v>0</v>
       </c>
       <c r="AU103" s="3" t="n">
-        <v>46172.875</v>
+        <v>46172.91666666666</v>
       </c>
     </row>
     <row r="104">
@@ -16896,7 +16896,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17046,7 +17046,7 @@
         <v>0</v>
       </c>
       <c r="AU104" s="3" t="n">
-        <v>46172.91666666666</v>
+        <v>46172.95833333334</v>
       </c>
     </row>
     <row r="105">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17214,12 +17214,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17364,7 +17364,7 @@
         <v>0</v>
       </c>
       <c r="AU106" s="3" t="n">
-        <v>46172.95833333334</v>
+        <v>46172.97916666666</v>
       </c>
     </row>
     <row r="107">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17523,165 +17523,6 @@
         <v>0</v>
       </c>
       <c r="AU107" s="3" t="n">
-        <v>46172.97916666666</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="n">
-        <v>46172</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Las Vegas Lights</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Tulsa Roughnecks</t>
-        </is>
-      </c>
-      <c r="G108" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N108" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
-      <c r="R108" t="n">
-        <v>0</v>
-      </c>
-      <c r="S108" t="n">
-        <v>0</v>
-      </c>
-      <c r="T108" t="n">
-        <v>0</v>
-      </c>
-      <c r="U108" t="n">
-        <v>0</v>
-      </c>
-      <c r="V108" t="n">
-        <v>0</v>
-      </c>
-      <c r="W108" t="n">
-        <v>0</v>
-      </c>
-      <c r="X108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM108" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN108" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO108" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP108" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU108" s="3" t="n">
         <v>46172.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,22 +11654,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,22 +11972,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G102" t="n">

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11972,22 +11972,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,10 +15869,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G105" t="n">

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,22 +10541,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11177,22 +11177,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G107" t="n">

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O46" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>3.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11177,22 +11177,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,10 +15869,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16664,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -10541,22 +10541,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,22 +11972,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="O77" t="n">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="P77" t="n">
-        <v>3.31</v>
+        <v>3.69</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="O78" t="n">
-        <v>3.54</v>
+        <v>3.33</v>
       </c>
       <c r="P78" t="n">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16664,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G105" t="n">

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O44" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P44" t="n">
-        <v>2.05</v>
+        <v>3.9</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P45" t="n">
-        <v>3.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,22 +10541,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,22 +11654,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,22 +11972,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="O77" t="n">
-        <v>3.54</v>
+        <v>3.33</v>
       </c>
       <c r="P77" t="n">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="O78" t="n">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="P78" t="n">
-        <v>3.31</v>
+        <v>3.69</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>2.01</v>
+        <v>1.61</v>
       </c>
       <c r="O92" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="P92" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G102" t="n">

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,17 +8512,17 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,22 +10541,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,22 +11654,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="O77" t="n">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="P77" t="n">
-        <v>3.31</v>
+        <v>3.69</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="O78" t="n">
-        <v>3.54</v>
+        <v>3.33</v>
       </c>
       <c r="P78" t="n">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -13961,10 +13961,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2.01</v>
+        <v>2.5</v>
       </c>
       <c r="O91" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P91" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,14 +15194,14 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="O93" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P93" t="n">
         <v>3.2</v>
       </c>
-      <c r="P93" t="n">
-        <v>2.55</v>
-      </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15710,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16664,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -16784,13 +16784,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -17420,13 +17420,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="O39" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P39" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.44</v>
+        <v>2.57</v>
       </c>
       <c r="O41" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="P41" t="n">
-        <v>6.63</v>
+        <v>2.53</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O47" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>3.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,17 +8512,17 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11177,22 +11177,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,22 +11972,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13802,10 +13802,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -13961,10 +13961,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14279,10 +14279,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14597,10 +14597,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>2.01</v>
+        <v>2.5</v>
       </c>
       <c r="O93" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P93" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="O94" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P94" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.57</v>
+        <v>1.86</v>
       </c>
       <c r="O41" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P41" t="n">
-        <v>2.53</v>
+        <v>4.1</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.86</v>
+        <v>2.65</v>
       </c>
       <c r="O43" t="n">
         <v>3.45</v>
       </c>
       <c r="P43" t="n">
-        <v>4.1</v>
+        <v>2.41</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -11177,22 +11177,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.29</v>
+        <v>1.92</v>
       </c>
       <c r="O68" t="n">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="P68" t="n">
-        <v>3.2</v>
+        <v>4.38</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11336,22 +11336,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>1.92</v>
+        <v>2.29</v>
       </c>
       <c r="O69" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="P69" t="n">
-        <v>4.38</v>
+        <v>3.2</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,22 +11972,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="O77" t="n">
-        <v>3.54</v>
+        <v>3.33</v>
       </c>
       <c r="P77" t="n">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="O78" t="n">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="P78" t="n">
-        <v>3.31</v>
+        <v>3.69</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13643,10 +13643,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13802,10 +13802,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14279,10 +14279,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14597,10 +14597,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>2.5</v>
+        <v>1.61</v>
       </c>
       <c r="O93" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P93" t="n">
-        <v>2.55</v>
+        <v>4.4</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>2.01</v>
+        <v>2.5</v>
       </c>
       <c r="O94" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P94" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="O95" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P95" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O106" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="P106" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17420,13 +17420,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O107" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P107" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -17459,10 +17459,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.44</v>
+        <v>2.57</v>
       </c>
       <c r="O38" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="P38" t="n">
-        <v>6.63</v>
+        <v>2.53</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,17 +8512,17 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,17 +8830,17 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,22 +10541,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11336,22 +11336,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2.29</v>
+        <v>1.92</v>
       </c>
       <c r="O69" t="n">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="P69" t="n">
-        <v>3.2</v>
+        <v>4.38</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11495,22 +11495,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="O77" t="n">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="P77" t="n">
-        <v>3.31</v>
+        <v>3.69</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="O78" t="n">
-        <v>3.54</v>
+        <v>3.33</v>
       </c>
       <c r="P78" t="n">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13643,10 +13643,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -13961,10 +13961,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="O93" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="P93" t="n">
-        <v>4.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,14 +15353,14 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="O94" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P94" t="n">
         <v>3.2</v>
       </c>
-      <c r="P94" t="n">
-        <v>2.55</v>
-      </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="O95" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P95" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,10 +15869,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="O102" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="P102" t="n">
-        <v>2.4</v>
+        <v>4.17</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16664,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O106" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P106" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17420,13 +17420,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O107" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="P107" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -17459,10 +17459,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="O18" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="O38" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P38" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.86</v>
+        <v>1.44</v>
       </c>
       <c r="O40" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="P40" t="n">
-        <v>4.1</v>
+        <v>6.63</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,17 +8512,17 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,22 +10541,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11177,22 +11177,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11495,22 +11495,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14279,10 +14279,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="O92" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P92" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="O93" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P93" t="n">
-        <v>2.55</v>
+        <v>3.9</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="O95" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="P95" t="n">
-        <v>4.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,10 +15869,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -16505,10 +16505,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="O102" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="P102" t="n">
-        <v>4.17</v>
+        <v>2.4</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16664,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.78</v>
+        <v>2.14</v>
       </c>
       <c r="O12" t="n">
-        <v>3.61</v>
+        <v>3.32</v>
       </c>
       <c r="P12" t="n">
-        <v>2.43</v>
+        <v>3.03</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.14</v>
+        <v>2.78</v>
       </c>
       <c r="O13" t="n">
-        <v>3.32</v>
+        <v>3.61</v>
       </c>
       <c r="P13" t="n">
-        <v>3.03</v>
+        <v>2.43</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="O16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="O18" t="n">
-        <v>3.3</v>
+        <v>3.84</v>
       </c>
       <c r="P18" t="n">
-        <v>2.95</v>
+        <v>3.9</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="O38" t="n">
-        <v>3.45</v>
+        <v>3.36</v>
       </c>
       <c r="P38" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="O39" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P39" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.44</v>
+        <v>1.86</v>
       </c>
       <c r="O40" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="P40" t="n">
-        <v>6.63</v>
+        <v>4.1</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11177,22 +11177,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11654,22 +11654,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1.92</v>
+        <v>1.31</v>
       </c>
       <c r="O73" t="n">
-        <v>3.44</v>
+        <v>5.34</v>
       </c>
       <c r="P73" t="n">
-        <v>4.38</v>
+        <v>10.7</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="O77" t="n">
-        <v>3.54</v>
+        <v>3.33</v>
       </c>
       <c r="P77" t="n">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="O78" t="n">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="P78" t="n">
-        <v>3.31</v>
+        <v>3.69</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14597,10 +14597,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="O92" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="P92" t="n">
-        <v>4.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="O93" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P93" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="O95" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P95" t="n">
-        <v>2.55</v>
+        <v>3.9</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16664,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O106" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="P106" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17420,13 +17420,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O107" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P107" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -17459,10 +17459,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="O18" t="n">
-        <v>3.84</v>
+        <v>3.35</v>
       </c>
       <c r="P18" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="O19" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="O38" t="n">
-        <v>3.36</v>
+        <v>3.45</v>
       </c>
       <c r="P38" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.65</v>
+        <v>1.44</v>
       </c>
       <c r="O39" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="P39" t="n">
-        <v>2.41</v>
+        <v>6.63</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.44</v>
+        <v>1.86</v>
       </c>
       <c r="O41" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="P41" t="n">
-        <v>6.63</v>
+        <v>4.1</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,22 +10541,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11654,22 +11654,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13802,10 +13802,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -13961,10 +13961,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14279,10 +14279,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14438,10 +14438,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,10 +15869,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O106" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P106" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17420,13 +17420,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O107" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="P107" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -17459,10 +17459,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.14</v>
+        <v>2.78</v>
       </c>
       <c r="O14" t="n">
-        <v>3.32</v>
+        <v>3.61</v>
       </c>
       <c r="P14" t="n">
-        <v>3.03</v>
+        <v>2.43</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="O19" t="n">
-        <v>3.3</v>
+        <v>3.84</v>
       </c>
       <c r="P19" t="n">
-        <v>2.95</v>
+        <v>3.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.57</v>
+        <v>2.9</v>
       </c>
       <c r="O37" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="P37" t="n">
-        <v>2.53</v>
+        <v>2.33</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="O38" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P38" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.86</v>
+        <v>2.65</v>
       </c>
       <c r="O41" t="n">
         <v>3.45</v>
       </c>
       <c r="P41" t="n">
-        <v>4.1</v>
+        <v>2.41</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>3.9</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,22 +10541,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11336,22 +11336,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1.31</v>
+        <v>1.92</v>
       </c>
       <c r="O73" t="n">
-        <v>5.34</v>
+        <v>3.44</v>
       </c>
       <c r="P73" t="n">
-        <v>10.7</v>
+        <v>4.38</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13802,10 +13802,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -13961,10 +13961,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14279,10 +14279,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14438,10 +14438,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14597,10 +14597,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2.01</v>
+        <v>1.61</v>
       </c>
       <c r="O91" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="P91" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="O93" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="P93" t="n">
-        <v>4.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="O94" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P94" t="n">
-        <v>2.55</v>
+        <v>3.9</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,10 +15869,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -16505,10 +16505,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16664,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="O18" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
-        <v>3.84</v>
+        <v>3.35</v>
       </c>
       <c r="P19" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="O20" t="n">
-        <v>3.3</v>
+        <v>3.84</v>
       </c>
       <c r="P20" t="n">
-        <v>2.95</v>
+        <v>3.9</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.9</v>
+        <v>2.57</v>
       </c>
       <c r="O37" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="P37" t="n">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.44</v>
+        <v>2.65</v>
       </c>
       <c r="O43" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="P43" t="n">
-        <v>6.63</v>
+        <v>2.41</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P46" t="n">
-        <v>2.05</v>
+        <v>3.9</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11336,22 +11336,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11972,22 +11972,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1.92</v>
+        <v>2.29</v>
       </c>
       <c r="O73" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="P73" t="n">
-        <v>4.38</v>
+        <v>3.2</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12530,10 +12530,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13802,10 +13802,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -13961,10 +13961,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14279,10 +14279,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14597,10 +14597,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>1.61</v>
+        <v>2.01</v>
       </c>
       <c r="O91" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="P91" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>2.01</v>
+        <v>1.61</v>
       </c>
       <c r="O92" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="P92" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="O18" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P18" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="O19" t="n">
-        <v>3.35</v>
+        <v>3.84</v>
       </c>
       <c r="P19" t="n">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.57</v>
+        <v>1.86</v>
       </c>
       <c r="O37" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P37" t="n">
-        <v>2.53</v>
+        <v>4.1</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.44</v>
+        <v>2.9</v>
       </c>
       <c r="O39" t="n">
-        <v>4.4</v>
+        <v>3.36</v>
       </c>
       <c r="P39" t="n">
-        <v>6.63</v>
+        <v>2.33</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="O42" t="n">
-        <v>3.36</v>
+        <v>3.45</v>
       </c>
       <c r="P42" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9662,10 +9662,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10139,10 +10139,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10298,10 +10298,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10457,10 +10457,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11495,22 +11495,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,22 +11972,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="O73" t="n">
-        <v>3.41</v>
+        <v>3.22</v>
       </c>
       <c r="P73" t="n">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="O77" t="n">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="P77" t="n">
-        <v>3.31</v>
+        <v>3.69</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="O78" t="n">
-        <v>3.54</v>
+        <v>3.33</v>
       </c>
       <c r="P78" t="n">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13643,10 +13643,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13802,10 +13802,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14597,10 +14597,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="O92" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P92" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,14 +15194,14 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="O93" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P93" t="n">
         <v>3.2</v>
       </c>
-      <c r="P93" t="n">
-        <v>2.55</v>
-      </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="O95" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P95" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,10 +15869,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="O98" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="P98" t="n">
-        <v>4.17</v>
+        <v>2.4</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16664,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O106" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="P106" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17420,13 +17420,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O107" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P107" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -17459,10 +17459,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="O19" t="n">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="P19" t="n">
-        <v>3.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.57</v>
+        <v>1.44</v>
       </c>
       <c r="O36" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="P36" t="n">
-        <v>2.53</v>
+        <v>6.63</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.9</v>
+        <v>1.86</v>
       </c>
       <c r="O39" t="n">
-        <v>3.36</v>
+        <v>3.45</v>
       </c>
       <c r="P39" t="n">
-        <v>2.33</v>
+        <v>4.1</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="O42" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P42" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,17 +8512,17 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9662,10 +9662,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="O61" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="P61" t="n">
-        <v>3.61</v>
+        <v>3.71</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10139,10 +10139,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="O63" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="P63" t="n">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10457,10 +10457,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11336,22 +11336,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11495,22 +11495,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,22 +11654,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="O77" t="n">
-        <v>3.54</v>
+        <v>3.33</v>
       </c>
       <c r="P77" t="n">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="O78" t="n">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="P78" t="n">
-        <v>3.31</v>
+        <v>3.69</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13643,10 +13643,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13802,10 +13802,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="O92" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P92" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="O95" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P95" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,10 +15869,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -16505,10 +16505,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O106" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P106" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17420,13 +17420,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O107" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="P107" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -17459,10 +17459,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>3.84</v>
+        <v>3.35</v>
       </c>
       <c r="P17" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="O20" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.9</v>
+        <v>2.57</v>
       </c>
       <c r="O35" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="P35" t="n">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.57</v>
+        <v>1.86</v>
       </c>
       <c r="O42" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P42" t="n">
-        <v>2.53</v>
+        <v>4.1</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,17 +8512,17 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,17 +8830,17 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9821,10 +9821,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="O61" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="P61" t="n">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10139,10 +10139,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>3.09</v>
+        <v>2.12</v>
       </c>
       <c r="O62" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="P62" t="n">
-        <v>2.44</v>
+        <v>3.71</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10298,10 +10298,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2.24</v>
+        <v>3.09</v>
       </c>
       <c r="O63" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="P63" t="n">
-        <v>3.61</v>
+        <v>2.44</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10457,10 +10457,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="O68" t="n">
-        <v>3.22</v>
+        <v>3.44</v>
       </c>
       <c r="P68" t="n">
-        <v>3.43</v>
+        <v>4.38</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11336,22 +11336,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,22 +11495,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,22 +11654,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="O71" t="n">
-        <v>3.41</v>
+        <v>3.22</v>
       </c>
       <c r="P71" t="n">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,22 +11813,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12530,10 +12530,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="O77" t="n">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="P77" t="n">
-        <v>3.31</v>
+        <v>3.69</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="O78" t="n">
-        <v>3.54</v>
+        <v>3.33</v>
       </c>
       <c r="P78" t="n">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14279,10 +14279,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14597,10 +14597,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="O93" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P93" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="O95" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P95" t="n">
-        <v>3.9</v>
+        <v>2.55</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="O99" t="n">
-        <v>2.99</v>
+        <v>3.42</v>
       </c>
       <c r="P99" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -16505,10 +16505,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16664,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.78</v>
+        <v>2.14</v>
       </c>
       <c r="O12" t="n">
-        <v>3.61</v>
+        <v>3.32</v>
       </c>
       <c r="P12" t="n">
-        <v>2.43</v>
+        <v>3.03</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P20" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.44</v>
+        <v>2.57</v>
       </c>
       <c r="O36" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="P36" t="n">
-        <v>6.63</v>
+        <v>2.53</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.86</v>
+        <v>2.9</v>
       </c>
       <c r="O42" t="n">
-        <v>3.45</v>
+        <v>3.36</v>
       </c>
       <c r="P42" t="n">
-        <v>4.1</v>
+        <v>2.33</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>4.19</v>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>4.63</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="O46" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="P46" t="n">
-        <v>3.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9821,10 +9821,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2.24</v>
+        <v>3.09</v>
       </c>
       <c r="O61" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="P61" t="n">
-        <v>3.61</v>
+        <v>2.44</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10139,10 +10139,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>3.09</v>
+        <v>2.24</v>
       </c>
       <c r="O63" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="P63" t="n">
-        <v>2.44</v>
+        <v>3.61</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10457,10 +10457,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,22 +11495,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>2.29</v>
+        <v>1.31</v>
       </c>
       <c r="O70" t="n">
-        <v>3.41</v>
+        <v>5.34</v>
       </c>
       <c r="P70" t="n">
-        <v>3.2</v>
+        <v>10.7</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="O71" t="n">
-        <v>3.22</v>
+        <v>3.44</v>
       </c>
       <c r="P71" t="n">
-        <v>3.43</v>
+        <v>4.38</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,22 +11813,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,22 +11972,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1.31</v>
+        <v>2.29</v>
       </c>
       <c r="O73" t="n">
-        <v>5.34</v>
+        <v>3.41</v>
       </c>
       <c r="P73" t="n">
-        <v>10.7</v>
+        <v>3.2</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13166,10 +13166,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14597,10 +14597,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="O93" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P93" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="O95" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P95" t="n">
-        <v>2.55</v>
+        <v>3.9</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="O99" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="P99" t="n">
-        <v>4.17</v>
+        <v>2.4</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="O100" t="n">
-        <v>2.99</v>
+        <v>3.42</v>
       </c>
       <c r="P100" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16664,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O106" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="P106" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17420,13 +17420,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O107" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P107" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -17459,10 +17459,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.99</v>
+        <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="P7" t="n">
-        <v>1.75</v>
+        <v>3.87</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.57</v>
+        <v>2.9</v>
       </c>
       <c r="O36" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="P36" t="n">
-        <v>2.53</v>
+        <v>2.33</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="O45" t="n">
-        <v>4.19</v>
+        <v>4.1</v>
       </c>
       <c r="P45" t="n">
-        <v>4.63</v>
+        <v>3.9</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3.25</v>
+        <v>1.6</v>
       </c>
       <c r="O46" t="n">
-        <v>4.09</v>
+        <v>4.19</v>
       </c>
       <c r="P46" t="n">
-        <v>1.91</v>
+        <v>4.63</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8084,10 +8084,10 @@
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="O49" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="P49" t="n">
-        <v>3.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,17 +8512,17 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9980,10 +9980,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>3.09</v>
+        <v>2.24</v>
       </c>
       <c r="O61" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="P61" t="n">
-        <v>2.44</v>
+        <v>3.61</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10139,10 +10139,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.12</v>
+        <v>3.09</v>
       </c>
       <c r="O62" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="P62" t="n">
-        <v>3.71</v>
+        <v>2.44</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10298,10 +10298,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="O63" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="P63" t="n">
-        <v>3.61</v>
+        <v>3.71</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10457,10 +10457,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="O64" t="n">
-        <v>3.06</v>
+        <v>3.44</v>
       </c>
       <c r="P64" t="n">
-        <v>3.2</v>
+        <v>4.38</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11654,22 +11654,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>1.92</v>
+        <v>2.29</v>
       </c>
       <c r="O71" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="P71" t="n">
-        <v>4.38</v>
+        <v>3.2</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11972,22 +11972,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,10 +12014,10 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="O73" t="n">
-        <v>3.41</v>
+        <v>3.06</v>
       </c>
       <c r="P73" t="n">
         <v>3.2</v>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13007,10 +13007,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13166,10 +13166,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>2.12</v>
+        <v>4.05</v>
       </c>
       <c r="O87" t="n">
-        <v>3.3</v>
+        <v>3.66</v>
       </c>
       <c r="P87" t="n">
-        <v>3.32</v>
+        <v>1.72</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14279,10 +14279,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="O93" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P93" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="O95" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P95" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>2.01</v>
+        <v>2.5</v>
       </c>
       <c r="O101" t="n">
-        <v>2.99</v>
+        <v>3.45</v>
       </c>
       <c r="P101" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -16505,10 +16505,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O106" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P106" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17420,13 +17420,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O107" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="P107" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -17459,10 +17459,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.6</v>
+        <v>3.65</v>
       </c>
       <c r="O29" t="n">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="P29" t="n">
-        <v>4.63</v>
+        <v>2.06</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.65</v>
+        <v>1.6</v>
       </c>
       <c r="O30" t="n">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>2.06</v>
+        <v>4.63</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.57</v>
+        <v>1.44</v>
       </c>
       <c r="O34" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="P34" t="n">
-        <v>2.53</v>
+        <v>6.63</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="O36" t="n">
-        <v>3.36</v>
+        <v>3.45</v>
       </c>
       <c r="P36" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.65</v>
+        <v>1.86</v>
       </c>
       <c r="O37" t="n">
         <v>3.45</v>
       </c>
       <c r="P37" t="n">
-        <v>2.41</v>
+        <v>4.1</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="O46" t="n">
-        <v>4.19</v>
+        <v>5.9</v>
       </c>
       <c r="P46" t="n">
-        <v>4.63</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7766,10 +7766,10 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="O48" t="n">
-        <v>5.9</v>
+        <v>4.19</v>
       </c>
       <c r="P48" t="n">
-        <v>8.550000000000001</v>
+        <v>4.63</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8084,10 +8084,10 @@
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9980,10 +9980,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2.24</v>
+        <v>3.09</v>
       </c>
       <c r="O61" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="P61" t="n">
-        <v>3.61</v>
+        <v>2.44</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10139,10 +10139,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>3.09</v>
+        <v>2.24</v>
       </c>
       <c r="O62" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="P62" t="n">
-        <v>2.44</v>
+        <v>3.61</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10298,10 +10298,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="O66" t="n">
-        <v>3.22</v>
+        <v>3.41</v>
       </c>
       <c r="P66" t="n">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,22 +11654,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="O71" t="n">
-        <v>3.41</v>
+        <v>3.22</v>
       </c>
       <c r="P71" t="n">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="O73" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="P73" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13643,10 +13643,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13802,10 +13802,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>2.12</v>
+        <v>4.05</v>
       </c>
       <c r="O86" t="n">
-        <v>3.3</v>
+        <v>3.66</v>
       </c>
       <c r="P86" t="n">
-        <v>3.32</v>
+        <v>1.72</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,49 +14240,49 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>4.05</v>
+        <v>2.12</v>
       </c>
       <c r="O87" t="n">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="P87" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB87" t="n">
         <v>1.72</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" t="n">
-        <v>0</v>
-      </c>
-      <c r="T87" t="n">
-        <v>0</v>
-      </c>
-      <c r="U87" t="n">
-        <v>0</v>
-      </c>
-      <c r="V87" t="n">
-        <v>0</v>
-      </c>
-      <c r="W87" t="n">
-        <v>0</v>
-      </c>
-      <c r="X87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB87" t="n">
-        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14597,10 +14597,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>2.01</v>
+        <v>1.61</v>
       </c>
       <c r="O92" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="P92" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="O93" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P93" t="n">
-        <v>3.9</v>
+        <v>2.55</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="O95" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P95" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -16505,10 +16505,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O106" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="P106" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17420,13 +17420,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O107" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P107" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -17459,10 +17459,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.52</v>
+        <v>1.84</v>
       </c>
       <c r="O6" t="n">
-        <v>3.22</v>
+        <v>3.36</v>
       </c>
       <c r="P6" t="n">
-        <v>1.98</v>
+        <v>3.87</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.99</v>
+        <v>3.52</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="P9" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="O17" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>6.14</v>
+        <v>1.98</v>
       </c>
       <c r="O22" t="n">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="P22" t="n">
-        <v>1.43</v>
+        <v>3.12</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.65</v>
+        <v>1.6</v>
       </c>
       <c r="O29" t="n">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>2.06</v>
+        <v>4.63</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O44" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P44" t="n">
-        <v>2.05</v>
+        <v>3.9</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P45" t="n">
-        <v>3.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="O46" t="n">
-        <v>5.9</v>
+        <v>4.19</v>
       </c>
       <c r="P46" t="n">
-        <v>8.550000000000001</v>
+        <v>4.63</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7766,10 +7766,10 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.6</v>
+        <v>3.25</v>
       </c>
       <c r="O48" t="n">
-        <v>4.19</v>
+        <v>4.09</v>
       </c>
       <c r="P48" t="n">
-        <v>4.63</v>
+        <v>1.91</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>3.25</v>
+        <v>1.23</v>
       </c>
       <c r="O49" t="n">
-        <v>4.09</v>
+        <v>5.9</v>
       </c>
       <c r="P49" t="n">
-        <v>1.91</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8243,10 +8243,10 @@
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.48</v>
+        <v>6.55</v>
       </c>
       <c r="O57" t="n">
-        <v>2.69</v>
+        <v>4.5</v>
       </c>
       <c r="P57" t="n">
-        <v>3.09</v>
+        <v>1.4</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9662,10 +9662,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="O62" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="P62" t="n">
-        <v>3.61</v>
+        <v>3.71</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10298,10 +10298,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="O63" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="P63" t="n">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10457,10 +10457,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="O65" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="P65" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11177,22 +11177,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="O69" t="n">
-        <v>3.44</v>
+        <v>3.06</v>
       </c>
       <c r="P69" t="n">
-        <v>4.38</v>
+        <v>3.2</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11417,10 +11417,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -11495,22 +11495,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="O71" t="n">
-        <v>3.22</v>
+        <v>3.44</v>
       </c>
       <c r="P71" t="n">
-        <v>3.43</v>
+        <v>4.38</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>1.31</v>
+        <v>2.14</v>
       </c>
       <c r="O72" t="n">
-        <v>5.34</v>
+        <v>3.22</v>
       </c>
       <c r="P72" t="n">
-        <v>10.7</v>
+        <v>3.43</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2.17</v>
+        <v>1.31</v>
       </c>
       <c r="O73" t="n">
-        <v>3.1</v>
+        <v>5.34</v>
       </c>
       <c r="P73" t="n">
-        <v>3.15</v>
+        <v>10.7</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="O77" t="n">
-        <v>3.54</v>
+        <v>3.33</v>
       </c>
       <c r="P77" t="n">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="O78" t="n">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="P78" t="n">
-        <v>3.31</v>
+        <v>3.69</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13007,10 +13007,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13166,10 +13166,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,49 +14081,49 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>4.05</v>
+        <v>2.12</v>
       </c>
       <c r="O86" t="n">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="P86" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" t="n">
+        <v>0</v>
+      </c>
+      <c r="W86" t="n">
+        <v>0</v>
+      </c>
+      <c r="X86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB86" t="n">
         <v>1.72</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" t="n">
-        <v>0</v>
-      </c>
-      <c r="S86" t="n">
-        <v>0</v>
-      </c>
-      <c r="T86" t="n">
-        <v>0</v>
-      </c>
-      <c r="U86" t="n">
-        <v>0</v>
-      </c>
-      <c r="V86" t="n">
-        <v>0</v>
-      </c>
-      <c r="W86" t="n">
-        <v>0</v>
-      </c>
-      <c r="X86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB86" t="n">
-        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14279,10 +14279,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>2.5</v>
+        <v>1.61</v>
       </c>
       <c r="O93" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P93" t="n">
-        <v>2.55</v>
+        <v>4.4</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>2.01</v>
+        <v>2.5</v>
       </c>
       <c r="O94" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P94" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="O99" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="P99" t="n">
-        <v>2.4</v>
+        <v>4.17</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16664,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.99</v>
+        <v>3.52</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="P7" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.52</v>
+        <v>3.99</v>
       </c>
       <c r="O9" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="O16" t="n">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>3.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="O17" t="n">
-        <v>3.3</v>
+        <v>3.84</v>
       </c>
       <c r="P17" t="n">
-        <v>2.95</v>
+        <v>3.9</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>6.14</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.86</v>
+        <v>2.65</v>
       </c>
       <c r="O40" t="n">
         <v>3.45</v>
       </c>
       <c r="P40" t="n">
-        <v>4.1</v>
+        <v>2.41</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.57</v>
+        <v>1.86</v>
       </c>
       <c r="O42" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P42" t="n">
-        <v>2.53</v>
+        <v>4.1</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="O44" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="P44" t="n">
-        <v>3.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>1.23</v>
       </c>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O48" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="P48" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.23</v>
+        <v>1.75</v>
       </c>
       <c r="O49" t="n">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="P49" t="n">
-        <v>8.550000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8243,10 +8243,10 @@
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,17 +8512,17 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>6.55</v>
+        <v>1.1</v>
       </c>
       <c r="O57" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="P57" t="n">
-        <v>1.4</v>
+        <v>16</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.48</v>
+        <v>6.55</v>
       </c>
       <c r="O58" t="n">
-        <v>2.69</v>
+        <v>4.5</v>
       </c>
       <c r="P58" t="n">
-        <v>3.09</v>
+        <v>1.4</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9662,10 +9662,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.1</v>
+        <v>6.34</v>
       </c>
       <c r="O59" t="n">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="P59" t="n">
-        <v>16</v>
+        <v>1.39</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>6.34</v>
+        <v>2.48</v>
       </c>
       <c r="O60" t="n">
-        <v>4.7</v>
+        <v>2.69</v>
       </c>
       <c r="P60" t="n">
-        <v>1.39</v>
+        <v>3.09</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9980,10 +9980,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>3.09</v>
+        <v>2.24</v>
       </c>
       <c r="O61" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="P61" t="n">
-        <v>2.44</v>
+        <v>3.61</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10139,10 +10139,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.12</v>
+        <v>3.09</v>
       </c>
       <c r="O62" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="P62" t="n">
-        <v>3.71</v>
+        <v>2.44</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10298,10 +10298,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="O63" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="P63" t="n">
-        <v>3.61</v>
+        <v>3.71</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10457,10 +10457,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11177,22 +11177,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11336,22 +11336,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11417,10 +11417,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="O71" t="n">
-        <v>3.44</v>
+        <v>3.22</v>
       </c>
       <c r="P71" t="n">
-        <v>4.38</v>
+        <v>3.43</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>2.14</v>
+        <v>1.31</v>
       </c>
       <c r="O72" t="n">
-        <v>3.22</v>
+        <v>5.34</v>
       </c>
       <c r="P72" t="n">
-        <v>3.43</v>
+        <v>10.7</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1.31</v>
+        <v>2.17</v>
       </c>
       <c r="O73" t="n">
-        <v>5.34</v>
+        <v>3.1</v>
       </c>
       <c r="P73" t="n">
-        <v>10.7</v>
+        <v>3.15</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13007,10 +13007,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13166,10 +13166,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13643,10 +13643,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13802,10 +13802,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2.01</v>
+        <v>2.5</v>
       </c>
       <c r="O91" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P91" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="O94" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P94" t="n">
-        <v>2.55</v>
+        <v>3.9</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="O95" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P95" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -16505,10 +16505,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16664,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="O16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P16" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.98</v>
+        <v>6.14</v>
       </c>
       <c r="O23" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="P23" t="n">
-        <v>3.12</v>
+        <v>1.43</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>6.14</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.9</v>
+        <v>1.86</v>
       </c>
       <c r="O36" t="n">
-        <v>3.36</v>
+        <v>3.45</v>
       </c>
       <c r="P36" t="n">
-        <v>2.33</v>
+        <v>4.1</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.57</v>
+        <v>1.44</v>
       </c>
       <c r="O38" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="P38" t="n">
-        <v>2.53</v>
+        <v>6.63</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="O40" t="n">
-        <v>3.45</v>
+        <v>3.36</v>
       </c>
       <c r="P40" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.44</v>
+        <v>2.65</v>
       </c>
       <c r="O43" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="P43" t="n">
-        <v>6.63</v>
+        <v>2.41</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="O45" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="P45" t="n">
-        <v>8.550000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="O46" t="n">
-        <v>4.19</v>
+        <v>4.1</v>
       </c>
       <c r="P46" t="n">
-        <v>4.63</v>
+        <v>3.9</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="O47" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="P47" t="n">
-        <v>7.6</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7925,10 +7925,10 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>4.19</v>
       </c>
       <c r="P48" t="n">
-        <v>2.05</v>
+        <v>4.63</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O49" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P49" t="n">
-        <v>3.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.1</v>
+        <v>2.48</v>
       </c>
       <c r="O57" t="n">
-        <v>7.8</v>
+        <v>2.69</v>
       </c>
       <c r="P57" t="n">
-        <v>16</v>
+        <v>3.09</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>6.55</v>
+        <v>6.34</v>
       </c>
       <c r="O58" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="P58" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>6.34</v>
+        <v>1.1</v>
       </c>
       <c r="O59" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="P59" t="n">
-        <v>1.39</v>
+        <v>16</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2.48</v>
+        <v>6.55</v>
       </c>
       <c r="O60" t="n">
-        <v>2.69</v>
+        <v>4.5</v>
       </c>
       <c r="P60" t="n">
-        <v>3.09</v>
+        <v>1.4</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9980,10 +9980,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11258,10 +11258,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -11336,22 +11336,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="O73" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="P73" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12530,10 +12530,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13007,10 +13007,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13166,10 +13166,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13643,10 +13643,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13802,10 +13802,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2.5</v>
+        <v>1.61</v>
       </c>
       <c r="O91" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P91" t="n">
-        <v>2.55</v>
+        <v>4.4</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="O94" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P94" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="O95" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P95" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>2.01</v>
+        <v>2.5</v>
       </c>
       <c r="O98" t="n">
-        <v>2.99</v>
+        <v>3.45</v>
       </c>
       <c r="P98" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -16505,10 +16505,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU107"/>
+  <dimension ref="A1:AU111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.98</v>
+        <v>6.14</v>
       </c>
       <c r="O22" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="P22" t="n">
-        <v>3.12</v>
+        <v>1.43</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>6.14</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="O41" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P41" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.65</v>
+        <v>1.44</v>
       </c>
       <c r="O43" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.41</v>
+        <v>6.63</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="O47" t="n">
-        <v>5.9</v>
+        <v>4.19</v>
       </c>
       <c r="P47" t="n">
-        <v>8.550000000000001</v>
+        <v>4.63</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7925,10 +7925,10 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="O48" t="n">
-        <v>4.19</v>
+        <v>4</v>
       </c>
       <c r="P48" t="n">
-        <v>4.63</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8310,12 +8310,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="AU50" s="3" t="n">
-        <v>46172.46875</v>
+        <v>46172.45833333334</v>
       </c>
     </row>
     <row r="51">
@@ -8469,27 +8469,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,17 +8512,17 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="AU51" s="3" t="n">
-        <v>46172.5</v>
+        <v>46172.45833333334</v>
       </c>
     </row>
     <row r="52">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.83</v>
+        <v>1.23</v>
       </c>
       <c r="O52" t="n">
-        <v>3.6</v>
+        <v>5.9</v>
       </c>
       <c r="P52" t="n">
-        <v>3.83</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8720,10 +8720,10 @@
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
@@ -8778,7 +8778,7 @@
         <v>0</v>
       </c>
       <c r="AU52" s="3" t="n">
-        <v>46172.5</v>
+        <v>46172.45833333334</v>
       </c>
     </row>
     <row r="53">
@@ -8787,27 +8787,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8937,7 +8937,7 @@
         <v>0</v>
       </c>
       <c r="AU53" s="3" t="n">
-        <v>46172.5</v>
+        <v>46172.45833333334</v>
       </c>
     </row>
     <row r="54">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="O54" t="n">
-        <v>3.64</v>
+        <v>3.57</v>
       </c>
       <c r="P54" t="n">
-        <v>3.37</v>
+        <v>2.85</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9096,7 +9096,7 @@
         <v>0</v>
       </c>
       <c r="AU54" s="3" t="n">
-        <v>46172.54166666666</v>
+        <v>46172.46875</v>
       </c>
     </row>
     <row r="55">
@@ -9105,27 +9105,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -9255,7 +9255,7 @@
         <v>0</v>
       </c>
       <c r="AU55" s="3" t="n">
-        <v>46172.5625</v>
+        <v>46172.5</v>
       </c>
     </row>
     <row r="56">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="O56" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P56" t="n">
-        <v>4.52</v>
+        <v>3.83</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9414,7 +9414,7 @@
         <v>0</v>
       </c>
       <c r="AU56" s="3" t="n">
-        <v>46172.60416666666</v>
+        <v>46172.5</v>
       </c>
     </row>
     <row r="57">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -9573,7 +9573,7 @@
         <v>0</v>
       </c>
       <c r="AU57" s="3" t="n">
-        <v>46172.625</v>
+        <v>46172.5</v>
       </c>
     </row>
     <row r="58">
@@ -9582,27 +9582,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>6.34</v>
+        <v>2.25</v>
       </c>
       <c r="O58" t="n">
-        <v>4.7</v>
+        <v>3.64</v>
       </c>
       <c r="P58" t="n">
-        <v>1.39</v>
+        <v>3.37</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9732,7 +9732,7 @@
         <v>0</v>
       </c>
       <c r="AU58" s="3" t="n">
-        <v>46172.625</v>
+        <v>46172.54166666666</v>
       </c>
     </row>
     <row r="59">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AU59" s="3" t="n">
-        <v>46172.625</v>
+        <v>46172.5625</v>
       </c>
     </row>
     <row r="60">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>6.55</v>
+        <v>1.62</v>
       </c>
       <c r="O60" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P60" t="n">
-        <v>1.4</v>
+        <v>4.52</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
         <v>0</v>
       </c>
       <c r="AU60" s="3" t="n">
-        <v>46172.625</v>
+        <v>46172.60416666666</v>
       </c>
     </row>
     <row r="61">
@@ -10059,12 +10059,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2.24</v>
+        <v>1.1</v>
       </c>
       <c r="O61" t="n">
-        <v>2.66</v>
+        <v>7.8</v>
       </c>
       <c r="P61" t="n">
-        <v>3.61</v>
+        <v>16</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10139,10 +10139,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="AU61" s="3" t="n">
-        <v>46172.64583333334</v>
+        <v>46172.625</v>
       </c>
     </row>
     <row r="62">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>3.09</v>
+        <v>6.55</v>
       </c>
       <c r="O62" t="n">
-        <v>2.73</v>
+        <v>4.5</v>
       </c>
       <c r="P62" t="n">
-        <v>2.44</v>
+        <v>1.4</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10298,10 +10298,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="AU62" s="3" t="n">
-        <v>46172.64583333334</v>
+        <v>46172.625</v>
       </c>
     </row>
     <row r="63">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2.12</v>
+        <v>6.34</v>
       </c>
       <c r="O63" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="P63" t="n">
-        <v>3.71</v>
+        <v>1.39</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10457,10 +10457,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -10527,7 +10527,7 @@
         <v>0</v>
       </c>
       <c r="AU63" s="3" t="n">
-        <v>46172.64583333334</v>
+        <v>46172.625</v>
       </c>
     </row>
     <row r="64">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10616,10 +10616,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -10686,7 +10686,7 @@
         <v>0</v>
       </c>
       <c r="AU64" s="3" t="n">
-        <v>46172.66666666666</v>
+        <v>46172.625</v>
       </c>
     </row>
     <row r="65">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2.14</v>
+        <v>3.09</v>
       </c>
       <c r="O65" t="n">
-        <v>3.22</v>
+        <v>2.73</v>
       </c>
       <c r="P65" t="n">
-        <v>3.43</v>
+        <v>2.44</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10775,10 +10775,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -10845,7 +10845,7 @@
         <v>0</v>
       </c>
       <c r="AU65" s="3" t="n">
-        <v>46172.66666666666</v>
+        <v>46172.64583333334</v>
       </c>
     </row>
     <row r="66">
@@ -10854,27 +10854,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10934,10 +10934,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -11004,7 +11004,7 @@
         <v>0</v>
       </c>
       <c r="AU66" s="3" t="n">
-        <v>46172.66666666666</v>
+        <v>46172.64583333334</v>
       </c>
     </row>
     <row r="67">
@@ -11013,12 +11013,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="O67" t="n">
-        <v>3.44</v>
+        <v>2.8</v>
       </c>
       <c r="P67" t="n">
-        <v>4.38</v>
+        <v>3.71</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11093,10 +11093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -11163,7 +11163,7 @@
         <v>0</v>
       </c>
       <c r="AU67" s="3" t="n">
-        <v>46172.66666666666</v>
+        <v>46172.64583333334</v>
       </c>
     </row>
     <row r="68">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11258,10 +11258,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11417,10 +11417,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -11495,22 +11495,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,22 +11654,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11813,22 +11813,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>1.31</v>
+        <v>2.29</v>
       </c>
       <c r="O72" t="n">
-        <v>5.34</v>
+        <v>3.41</v>
       </c>
       <c r="P72" t="n">
-        <v>10.7</v>
+        <v>3.2</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2.3</v>
+        <v>1.31</v>
       </c>
       <c r="O73" t="n">
-        <v>3.06</v>
+        <v>5.34</v>
       </c>
       <c r="P73" t="n">
-        <v>3.2</v>
+        <v>10.7</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -12126,12 +12126,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12276,7 +12276,7 @@
         <v>0</v>
       </c>
       <c r="AU74" s="3" t="n">
-        <v>46172.70833333334</v>
+        <v>46172.66666666666</v>
       </c>
     </row>
     <row r="75">
@@ -12285,12 +12285,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12435,7 +12435,7 @@
         <v>0</v>
       </c>
       <c r="AU75" s="3" t="n">
-        <v>46172.70833333334</v>
+        <v>46172.66666666666</v>
       </c>
     </row>
     <row r="76">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12530,10 +12530,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -12594,7 +12594,7 @@
         <v>0</v>
       </c>
       <c r="AU76" s="3" t="n">
-        <v>46172.70833333334</v>
+        <v>46172.66666666666</v>
       </c>
     </row>
     <row r="77">
@@ -12603,12 +12603,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="O77" t="n">
-        <v>3.33</v>
+        <v>3.06</v>
       </c>
       <c r="P77" t="n">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12689,10 +12689,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -12753,7 +12753,7 @@
         <v>0</v>
       </c>
       <c r="AU77" s="3" t="n">
-        <v>46172.72916666666</v>
+        <v>46172.66666666666</v>
       </c>
     </row>
     <row r="78">
@@ -12762,12 +12762,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2.05</v>
+        <v>2.42</v>
       </c>
       <c r="O78" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="P78" t="n">
-        <v>3.69</v>
+        <v>2.84</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12848,10 +12848,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -12912,7 +12912,7 @@
         <v>0</v>
       </c>
       <c r="AU78" s="3" t="n">
-        <v>46172.72916666666</v>
+        <v>46172.70833333334</v>
       </c>
     </row>
     <row r="79">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13071,7 +13071,7 @@
         <v>0</v>
       </c>
       <c r="AU79" s="3" t="n">
-        <v>46172.75</v>
+        <v>46172.70833333334</v>
       </c>
     </row>
     <row r="80">
@@ -13080,12 +13080,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13166,10 +13166,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -13230,7 +13230,7 @@
         <v>0</v>
       </c>
       <c r="AU80" s="3" t="n">
-        <v>46172.75</v>
+        <v>46172.70833333334</v>
       </c>
     </row>
     <row r="81">
@@ -13239,12 +13239,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13389,7 +13389,7 @@
         <v>0</v>
       </c>
       <c r="AU81" s="3" t="n">
-        <v>46172.75</v>
+        <v>46172.72916666666</v>
       </c>
     </row>
     <row r="82">
@@ -13398,12 +13398,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13445,13 +13445,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13548,7 +13548,7 @@
         <v>0</v>
       </c>
       <c r="AU82" s="3" t="n">
-        <v>46172.76041666666</v>
+        <v>46172.72916666666</v>
       </c>
     </row>
     <row r="83">
@@ -13557,12 +13557,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>1.69</v>
+        <v>3.02</v>
       </c>
       <c r="O83" t="n">
-        <v>3.74</v>
+        <v>3.08</v>
       </c>
       <c r="P83" t="n">
-        <v>4.73</v>
+        <v>2.4</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13643,10 +13643,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -13707,7 +13707,7 @@
         <v>0</v>
       </c>
       <c r="AU83" s="3" t="n">
-        <v>46172.77083333334</v>
+        <v>46172.75</v>
       </c>
     </row>
     <row r="84">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13866,7 +13866,7 @@
         <v>0</v>
       </c>
       <c r="AU84" s="3" t="n">
-        <v>46172.77083333334</v>
+        <v>46172.75</v>
       </c>
     </row>
     <row r="85">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14025,7 +14025,7 @@
         <v>0</v>
       </c>
       <c r="AU85" s="3" t="n">
-        <v>46172.77083333334</v>
+        <v>46172.75</v>
       </c>
     </row>
     <row r="86">
@@ -14034,12 +14034,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="AU86" s="3" t="n">
-        <v>46172.79166666666</v>
+        <v>46172.76041666666</v>
       </c>
     </row>
     <row r="87">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14343,7 +14343,7 @@
         <v>0</v>
       </c>
       <c r="AU87" s="3" t="n">
-        <v>46172.79166666666</v>
+        <v>46172.77083333334</v>
       </c>
     </row>
     <row r="88">
@@ -14352,12 +14352,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14502,7 +14502,7 @@
         <v>0</v>
       </c>
       <c r="AU88" s="3" t="n">
-        <v>46172.79166666666</v>
+        <v>46172.77083333334</v>
       </c>
     </row>
     <row r="89">
@@ -14511,12 +14511,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="O89" t="n">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="P89" t="n">
-        <v>5.63</v>
+        <v>4.73</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14597,10 +14597,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -14661,7 +14661,7 @@
         <v>0</v>
       </c>
       <c r="AU89" s="3" t="n">
-        <v>46172.8125</v>
+        <v>46172.77083333334</v>
       </c>
     </row>
     <row r="90">
@@ -14670,12 +14670,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14820,7 +14820,7 @@
         <v>0</v>
       </c>
       <c r="AU90" s="3" t="n">
-        <v>46172.8125</v>
+        <v>46172.79166666666</v>
       </c>
     </row>
     <row r="91">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>1.61</v>
+        <v>2.12</v>
       </c>
       <c r="O91" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P91" t="n">
-        <v>4.4</v>
+        <v>3.32</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -14979,7 +14979,7 @@
         <v>0</v>
       </c>
       <c r="AU91" s="3" t="n">
-        <v>46172.83333333334</v>
+        <v>46172.79166666666</v>
       </c>
     </row>
     <row r="92">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15138,7 +15138,7 @@
         <v>0</v>
       </c>
       <c r="AU92" s="3" t="n">
-        <v>46172.83333333334</v>
+        <v>46172.79166666666</v>
       </c>
     </row>
     <row r="93">
@@ -15147,12 +15147,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>2.5</v>
+        <v>1.51</v>
       </c>
       <c r="O93" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P93" t="n">
-        <v>2.55</v>
+        <v>5.63</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15297,7 +15297,7 @@
         <v>0</v>
       </c>
       <c r="AU93" s="3" t="n">
-        <v>46172.83333333334</v>
+        <v>46172.8125</v>
       </c>
     </row>
     <row r="94">
@@ -15306,12 +15306,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15456,7 +15456,7 @@
         <v>0</v>
       </c>
       <c r="AU94" s="3" t="n">
-        <v>46172.83333333334</v>
+        <v>46172.8125</v>
       </c>
     </row>
     <row r="95">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15624,12 +15624,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="O96" t="n">
         <v>3.2</v>
       </c>
       <c r="P96" t="n">
-        <v>3.24</v>
+        <v>2.55</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15710,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -15774,7 +15774,7 @@
         <v>0</v>
       </c>
       <c r="AU96" s="3" t="n">
-        <v>46172.85416666666</v>
+        <v>46172.83333333334</v>
       </c>
     </row>
     <row r="97">
@@ -15783,12 +15783,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,10 +15869,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -15933,7 +15933,7 @@
         <v>0</v>
       </c>
       <c r="AU97" s="3" t="n">
-        <v>46172.875</v>
+        <v>46172.83333333334</v>
       </c>
     </row>
     <row r="98">
@@ -15942,7 +15942,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="O98" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P98" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16092,7 +16092,7 @@
         <v>0</v>
       </c>
       <c r="AU98" s="3" t="n">
-        <v>46172.875</v>
+        <v>46172.83333333334</v>
       </c>
     </row>
     <row r="99">
@@ -16101,12 +16101,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16251,7 +16251,7 @@
         <v>0</v>
       </c>
       <c r="AU99" s="3" t="n">
-        <v>46172.875</v>
+        <v>46172.83333333334</v>
       </c>
     </row>
     <row r="100">
@@ -16260,12 +16260,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="O100" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="P100" t="n">
-        <v>4.17</v>
+        <v>3.24</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16410,7 +16410,7 @@
         <v>0</v>
       </c>
       <c r="AU100" s="3" t="n">
-        <v>46172.875</v>
+        <v>46172.85416666666</v>
       </c>
     </row>
     <row r="101">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16784,13 +16784,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
         <v>0</v>
       </c>
       <c r="AU103" s="3" t="n">
-        <v>46172.91666666666</v>
+        <v>46172.875</v>
       </c>
     </row>
     <row r="104">
@@ -16896,7 +16896,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="O104" t="n">
         <v>3.45</v>
       </c>
       <c r="P104" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -16982,10 +16982,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -17046,7 +17046,7 @@
         <v>0</v>
       </c>
       <c r="AU104" s="3" t="n">
-        <v>46172.95833333334</v>
+        <v>46172.875</v>
       </c>
     </row>
     <row r="105">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -17141,10 +17141,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -17205,7 +17205,7 @@
         <v>0</v>
       </c>
       <c r="AU105" s="3" t="n">
-        <v>46172.95833333334</v>
+        <v>46172.875</v>
       </c>
     </row>
     <row r="106">
@@ -17214,12 +17214,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -17364,7 +17364,7 @@
         <v>0</v>
       </c>
       <c r="AU106" s="3" t="n">
-        <v>46172.97916666666</v>
+        <v>46172.875</v>
       </c>
     </row>
     <row r="107">
@@ -17373,156 +17373,792 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Lexington</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O107" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P107" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU107" s="3" t="n">
+        <v>46172.91666666666</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Monterey Bay</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Loudoun United</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O108" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P108" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM108" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP108" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU108" s="3" t="n">
+        <v>46172.95833333334</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>LA Galaxy II</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Whitecaps II</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" t="n">
+        <v>0</v>
+      </c>
+      <c r="X109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU109" s="3" t="n">
+        <v>46172.95833333334</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Phoenix Rising</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O110" t="n">
+        <v>3</v>
+      </c>
+      <c r="P110" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" t="n">
+        <v>0</v>
+      </c>
+      <c r="X110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU110" s="3" t="n">
+        <v>46172.97916666666</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
         <is>
           <t>Las Vegas Lights</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>Tulsa Roughnecks</t>
         </is>
       </c>
-      <c r="G107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" t="inlineStr">
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N107" t="n">
+      <c r="N111" t="n">
         <v>2.3</v>
       </c>
-      <c r="O107" t="n">
+      <c r="O111" t="n">
         <v>3.35</v>
       </c>
-      <c r="P107" t="n">
+      <c r="P111" t="n">
         <v>2.65</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" t="n">
-        <v>0</v>
-      </c>
-      <c r="T107" t="n">
-        <v>0</v>
-      </c>
-      <c r="U107" t="n">
-        <v>0</v>
-      </c>
-      <c r="V107" t="n">
-        <v>0</v>
-      </c>
-      <c r="W107" t="n">
-        <v>0</v>
-      </c>
-      <c r="X107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA107" t="n">
+      <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" t="n">
+        <v>0</v>
+      </c>
+      <c r="X111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA111" t="n">
         <v>1.92</v>
       </c>
-      <c r="AB107" t="n">
+      <c r="AB111" t="n">
         <v>1.76</v>
       </c>
-      <c r="AC107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM107" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN107" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO107" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP107" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU107" s="3" t="n">
+      <c r="AC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU111" s="3" t="n">
         <v>46172.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU111"/>
+  <dimension ref="A1:AU112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.78</v>
+        <v>2.14</v>
       </c>
       <c r="O12" t="n">
-        <v>3.61</v>
+        <v>3.32</v>
       </c>
       <c r="P12" t="n">
-        <v>2.43</v>
+        <v>3.03</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="O17" t="n">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="P17" t="n">
-        <v>3.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>6.14</v>
+        <v>1.98</v>
       </c>
       <c r="O22" t="n">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="P22" t="n">
-        <v>1.43</v>
+        <v>3.12</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.57</v>
+        <v>2.9</v>
       </c>
       <c r="O37" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="P37" t="n">
-        <v>2.53</v>
+        <v>2.33</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.9</v>
+        <v>1.44</v>
       </c>
       <c r="O39" t="n">
-        <v>3.36</v>
+        <v>4.4</v>
       </c>
       <c r="P39" t="n">
-        <v>2.33</v>
+        <v>6.63</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,49 +7085,49 @@
         </is>
       </c>
       <c r="N42" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB42" t="n">
         <v>1.86</v>
-      </c>
-      <c r="O42" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="P42" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>3.25</v>
+        <v>1.6</v>
       </c>
       <c r="O44" t="n">
-        <v>4.09</v>
+        <v>4.19</v>
       </c>
       <c r="P44" t="n">
-        <v>1.91</v>
+        <v>4.63</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="O46" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="P46" t="n">
-        <v>3.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.43</v>
+        <v>2.09</v>
       </c>
       <c r="O54" t="n">
-        <v>3.57</v>
+        <v>3.4</v>
       </c>
       <c r="P54" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9105,12 +9105,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9148,17 +9148,17 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9255,7 +9255,7 @@
         <v>0</v>
       </c>
       <c r="AU55" s="3" t="n">
-        <v>46172.5</v>
+        <v>46172.46875</v>
       </c>
     </row>
     <row r="56">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9582,12 +9582,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9625,17 +9625,17 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9732,7 +9732,7 @@
         <v>0</v>
       </c>
       <c r="AU58" s="3" t="n">
-        <v>46172.54166666666</v>
+        <v>46172.5</v>
       </c>
     </row>
     <row r="59">
@@ -9741,27 +9741,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AU59" s="3" t="n">
-        <v>46172.5625</v>
+        <v>46172.54166666666</v>
       </c>
     </row>
     <row r="60">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
         <v>0</v>
       </c>
       <c r="AU60" s="3" t="n">
-        <v>46172.60416666666</v>
+        <v>46172.5625</v>
       </c>
     </row>
     <row r="61">
@@ -10059,12 +10059,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.1</v>
+        <v>1.62</v>
       </c>
       <c r="O61" t="n">
-        <v>7.8</v>
+        <v>4</v>
       </c>
       <c r="P61" t="n">
-        <v>16</v>
+        <v>4.52</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="AU61" s="3" t="n">
-        <v>46172.625</v>
+        <v>46172.60416666666</v>
       </c>
     </row>
     <row r="62">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>6.55</v>
+        <v>1.1</v>
       </c>
       <c r="O62" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="P62" t="n">
-        <v>1.4</v>
+        <v>16</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>6.34</v>
+        <v>6.55</v>
       </c>
       <c r="O63" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="P63" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2.48</v>
+        <v>6.34</v>
       </c>
       <c r="O64" t="n">
-        <v>2.69</v>
+        <v>4.7</v>
       </c>
       <c r="P64" t="n">
-        <v>3.09</v>
+        <v>1.39</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10616,10 +10616,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,14 +10742,14 @@
         </is>
       </c>
       <c r="N65" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O65" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P65" t="n">
         <v>3.09</v>
       </c>
-      <c r="O65" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="P65" t="n">
-        <v>2.44</v>
-      </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
@@ -10775,10 +10775,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -10845,7 +10845,7 @@
         <v>0</v>
       </c>
       <c r="AU65" s="3" t="n">
-        <v>46172.64583333334</v>
+        <v>46172.625</v>
       </c>
     </row>
     <row r="66">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.24</v>
+        <v>3.09</v>
       </c>
       <c r="O66" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="P66" t="n">
-        <v>3.61</v>
+        <v>2.44</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10934,10 +10934,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="O67" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="P67" t="n">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11093,10 +11093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -11172,12 +11172,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11252,10 +11252,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -11322,7 +11322,7 @@
         <v>0</v>
       </c>
       <c r="AU68" s="3" t="n">
-        <v>46172.66666666666</v>
+        <v>46172.64583333334</v>
       </c>
     </row>
     <row r="69">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11417,10 +11417,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11654,22 +11654,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11735,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="O74" t="n">
-        <v>3.22</v>
+        <v>3.44</v>
       </c>
       <c r="P74" t="n">
-        <v>3.43</v>
+        <v>4.38</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12290,22 +12290,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12689,10 +12689,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -12762,12 +12762,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="O78" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="P78" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12848,10 +12848,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -12912,7 +12912,7 @@
         <v>0</v>
       </c>
       <c r="AU78" s="3" t="n">
-        <v>46172.70833333334</v>
+        <v>46172.66666666666</v>
       </c>
     </row>
     <row r="79">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13166,10 +13166,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -13239,12 +13239,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13389,7 +13389,7 @@
         <v>0</v>
       </c>
       <c r="AU81" s="3" t="n">
-        <v>46172.72916666666</v>
+        <v>46172.70833333334</v>
       </c>
     </row>
     <row r="82">
@@ -13557,12 +13557,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>3.02</v>
+        <v>2.05</v>
       </c>
       <c r="O83" t="n">
-        <v>3.08</v>
+        <v>3.54</v>
       </c>
       <c r="P83" t="n">
-        <v>2.4</v>
+        <v>3.69</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13643,10 +13643,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -13707,7 +13707,7 @@
         <v>0</v>
       </c>
       <c r="AU83" s="3" t="n">
-        <v>46172.75</v>
+        <v>46172.72916666666</v>
       </c>
     </row>
     <row r="84">
@@ -14034,12 +14034,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="AU86" s="3" t="n">
-        <v>46172.76041666666</v>
+        <v>46172.75</v>
       </c>
     </row>
     <row r="87">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14343,7 +14343,7 @@
         <v>0</v>
       </c>
       <c r="AU87" s="3" t="n">
-        <v>46172.77083333334</v>
+        <v>46172.76041666666</v>
       </c>
     </row>
     <row r="88">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14438,10 +14438,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14597,10 +14597,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -14670,12 +14670,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14820,7 +14820,7 @@
         <v>0</v>
       </c>
       <c r="AU90" s="3" t="n">
-        <v>46172.79166666666</v>
+        <v>46172.77083333334</v>
       </c>
     </row>
     <row r="91">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15147,12 +15147,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1.51</v>
+        <v>4.05</v>
       </c>
       <c r="O93" t="n">
-        <v>4</v>
+        <v>3.66</v>
       </c>
       <c r="P93" t="n">
-        <v>5.63</v>
+        <v>1.72</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15297,7 +15297,7 @@
         <v>0</v>
       </c>
       <c r="AU93" s="3" t="n">
-        <v>46172.8125</v>
+        <v>46172.79166666666</v>
       </c>
     </row>
     <row r="94">
@@ -15465,12 +15465,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15615,7 +15615,7 @@
         <v>0</v>
       </c>
       <c r="AU95" s="3" t="n">
-        <v>46172.83333333334</v>
+        <v>46172.8125</v>
       </c>
     </row>
     <row r="96">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>2.5</v>
+        <v>1.61</v>
       </c>
       <c r="O96" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P96" t="n">
-        <v>2.55</v>
+        <v>4.4</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15710,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="O97" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P97" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,10 +15869,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="O99" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P99" t="n">
-        <v>3.9</v>
+        <v>2.55</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16260,12 +16260,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16410,7 +16410,7 @@
         <v>0</v>
       </c>
       <c r="AU100" s="3" t="n">
-        <v>46172.85416666666</v>
+        <v>46172.83333333334</v>
       </c>
     </row>
     <row r="101">
@@ -16419,12 +16419,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -16505,10 +16505,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
         <v>0</v>
       </c>
       <c r="AU101" s="3" t="n">
-        <v>46172.875</v>
+        <v>46172.85416666666</v>
       </c>
     </row>
     <row r="102">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="O102" t="n">
-        <v>2.99</v>
+        <v>3.42</v>
       </c>
       <c r="P102" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16664,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16784,13 +16784,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
@@ -16823,10 +16823,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -16982,10 +16982,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -17141,10 +17141,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17373,12 +17373,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17420,13 +17420,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>2.47</v>
+        <v>2.01</v>
       </c>
       <c r="O107" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="P107" t="n">
-        <v>2.87</v>
+        <v>4.2</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -17523,7 +17523,7 @@
         <v>0</v>
       </c>
       <c r="AU107" s="3" t="n">
-        <v>46172.91666666666</v>
+        <v>46172.875</v>
       </c>
     </row>
     <row r="108">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -17547,12 +17547,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -17579,13 +17579,13 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="O108" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P108" t="n">
-        <v>2.2</v>
+        <v>2.87</v>
       </c>
       <c r="Q108" t="n">
         <v>0</v>
@@ -17682,7 +17682,7 @@
         <v>0</v>
       </c>
       <c r="AU108" s="3" t="n">
-        <v>46172.95833333334</v>
+        <v>46172.91666666666</v>
       </c>
     </row>
     <row r="109">
@@ -17850,7 +17850,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -17897,13 +17897,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O110" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P110" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
@@ -18000,7 +18000,7 @@
         <v>0</v>
       </c>
       <c r="AU110" s="3" t="n">
-        <v>46172.97916666666</v>
+        <v>46172.95833333334</v>
       </c>
     </row>
     <row r="111">
@@ -18024,141 +18024,300 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
+          <t>Phoenix Rising</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O111" t="n">
+        <v>3</v>
+      </c>
+      <c r="P111" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" t="n">
+        <v>0</v>
+      </c>
+      <c r="X111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU111" s="3" t="n">
+        <v>46172.97916666666</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
           <t>Las Vegas Lights</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>Tulsa Roughnecks</t>
         </is>
       </c>
-      <c r="G111" t="n">
-        <v>0</v>
-      </c>
-      <c r="H111" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" t="n">
-        <v>0</v>
-      </c>
-      <c r="K111" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" t="inlineStr">
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N111" t="n">
+      <c r="N112" t="n">
         <v>2.3</v>
       </c>
-      <c r="O111" t="n">
+      <c r="O112" t="n">
         <v>3.35</v>
       </c>
-      <c r="P111" t="n">
+      <c r="P112" t="n">
         <v>2.65</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
-      <c r="R111" t="n">
-        <v>0</v>
-      </c>
-      <c r="S111" t="n">
-        <v>0</v>
-      </c>
-      <c r="T111" t="n">
-        <v>0</v>
-      </c>
-      <c r="U111" t="n">
-        <v>0</v>
-      </c>
-      <c r="V111" t="n">
-        <v>0</v>
-      </c>
-      <c r="W111" t="n">
-        <v>0</v>
-      </c>
-      <c r="X111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA111" t="n">
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" t="n">
+        <v>0</v>
+      </c>
+      <c r="X112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA112" t="n">
         <v>1.92</v>
       </c>
-      <c r="AB111" t="n">
+      <c r="AB112" t="n">
         <v>1.76</v>
       </c>
-      <c r="AC111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM111" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN111" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO111" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP111" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU111" s="3" t="n">
+      <c r="AC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU112" s="3" t="n">
         <v>46172.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.52</v>
+        <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>3.22</v>
+        <v>3.36</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>3.87</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>6.14</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="O40" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P40" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="O42" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P42" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7925,10 +7925,10 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="P48" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="O49" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="P49" t="n">
-        <v>3.9</v>
+        <v>7.6</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8720,10 +8720,10 @@
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.09</v>
+        <v>2.43</v>
       </c>
       <c r="O54" t="n">
-        <v>3.4</v>
+        <v>3.57</v>
       </c>
       <c r="P54" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.43</v>
+        <v>2.09</v>
       </c>
       <c r="O55" t="n">
-        <v>3.57</v>
+        <v>3.4</v>
       </c>
       <c r="P55" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>6.55</v>
+        <v>6.34</v>
       </c>
       <c r="O63" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="P63" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>6.34</v>
+        <v>6.55</v>
       </c>
       <c r="O64" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="P64" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>3.09</v>
+        <v>2.12</v>
       </c>
       <c r="O66" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="P66" t="n">
-        <v>2.44</v>
+        <v>3.71</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10934,10 +10934,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.24</v>
+        <v>3.09</v>
       </c>
       <c r="O67" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="P67" t="n">
-        <v>3.61</v>
+        <v>2.44</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11093,10 +11093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="O68" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="P68" t="n">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11252,10 +11252,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="Z68" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11735,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -11813,22 +11813,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="O72" t="n">
-        <v>3.41</v>
+        <v>3.1</v>
       </c>
       <c r="P72" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11894,10 +11894,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="O76" t="n">
-        <v>3.22</v>
+        <v>3.06</v>
       </c>
       <c r="P76" t="n">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12530,10 +12530,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -12608,22 +12608,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12848,10 +12848,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13166,10 +13166,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13325,10 +13325,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14438,10 +14438,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>2.12</v>
+        <v>4.05</v>
       </c>
       <c r="O92" t="n">
-        <v>3.3</v>
+        <v>3.66</v>
       </c>
       <c r="P92" t="n">
-        <v>3.32</v>
+        <v>1.72</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,49 +15194,49 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>4.05</v>
+        <v>2.12</v>
       </c>
       <c r="O93" t="n">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="P93" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" t="n">
+        <v>0</v>
+      </c>
+      <c r="X93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB93" t="n">
         <v>1.72</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
-      <c r="R93" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" t="n">
-        <v>0</v>
-      </c>
-      <c r="U93" t="n">
-        <v>0</v>
-      </c>
-      <c r="V93" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" t="n">
-        <v>0</v>
-      </c>
-      <c r="X93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB93" t="n">
-        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15710,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="O97" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P97" t="n">
-        <v>3.9</v>
+        <v>2.55</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,10 +15869,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="O98" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P98" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,14 +16148,14 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="O99" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P99" t="n">
         <v>3.2</v>
       </c>
-      <c r="P99" t="n">
-        <v>2.55</v>
-      </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="O102" t="n">
-        <v>3.42</v>
+        <v>2.99</v>
       </c>
       <c r="P102" t="n">
-        <v>4.17</v>
+        <v>4.2</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16664,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16784,13 +16784,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
@@ -16823,10 +16823,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -16982,10 +16982,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -17141,10 +17141,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17420,13 +17420,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18056,13 +18056,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O111" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P111" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
@@ -18095,10 +18095,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18215,13 +18215,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O112" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="P112" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
@@ -18254,10 +18254,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.99</v>
+        <v>1.84</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="P8" t="n">
-        <v>1.75</v>
+        <v>3.87</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.52</v>
+        <v>3.31</v>
       </c>
       <c r="O9" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>1.98</v>
+        <v>1.76</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF12" t="n">
         <v>1.91</v>
       </c>
-      <c r="AB12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="O18" t="n">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="P18" t="n">
-        <v>3.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P20" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="O21" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P21" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4868,55 +4868,55 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5345,55 +5345,55 @@
         <v>4.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="O33" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P33" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.86</v>
+        <v>2.65</v>
       </c>
       <c r="O36" t="n">
         <v>3.45</v>
       </c>
       <c r="P36" t="n">
-        <v>4.1</v>
+        <v>2.41</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,22 +6407,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.44</v>
+        <v>2.57</v>
       </c>
       <c r="O39" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="P39" t="n">
-        <v>6.63</v>
+        <v>2.53</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="O47" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="P47" t="n">
-        <v>8.550000000000001</v>
+        <v>6</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>3.25</v>
+        <v>1.6</v>
       </c>
       <c r="O48" t="n">
-        <v>4.09</v>
+        <v>4.19</v>
       </c>
       <c r="P48" t="n">
-        <v>1.91</v>
+        <v>4.63</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="O49" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="P49" t="n">
-        <v>7.6</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8720,10 +8720,10 @@
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="O53" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="P53" t="n">
-        <v>3.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.43</v>
+        <v>2.09</v>
       </c>
       <c r="O54" t="n">
-        <v>3.57</v>
+        <v>3.4</v>
       </c>
       <c r="P54" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.09</v>
+        <v>2.43</v>
       </c>
       <c r="O55" t="n">
-        <v>3.4</v>
+        <v>3.57</v>
       </c>
       <c r="P55" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9466,17 +9466,17 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="O66" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="P66" t="n">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10934,10 +10934,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="O68" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="P68" t="n">
-        <v>3.61</v>
+        <v>3.71</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11252,10 +11252,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11654,22 +11654,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11894,10 +11894,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1.31</v>
+        <v>2.3</v>
       </c>
       <c r="O73" t="n">
-        <v>5.34</v>
+        <v>3.06</v>
       </c>
       <c r="P73" t="n">
-        <v>10.7</v>
+        <v>3.2</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -12131,22 +12131,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12290,22 +12290,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12371,10 +12371,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12530,10 +12530,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -12608,22 +12608,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.29</v>
+        <v>1.92</v>
       </c>
       <c r="O77" t="n">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="P77" t="n">
-        <v>3.2</v>
+        <v>4.38</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13166,10 +13166,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13325,10 +13325,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14597,10 +14597,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14756,10 +14756,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15710,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="O98" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P98" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="O104" t="n">
-        <v>3.45</v>
+        <v>2.99</v>
       </c>
       <c r="P104" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -16982,10 +16982,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -17141,10 +17141,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17420,13 +17420,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -17459,10 +17459,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -17696,7 +17696,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -17738,13 +17738,13 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -17897,13 +17897,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18056,13 +18056,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O111" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="P111" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
@@ -18095,10 +18095,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18215,13 +18215,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O112" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P112" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
@@ -18254,10 +18254,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="O18" t="n">
         <v>3.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
         <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O20" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>6.14</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P24" t="n">
-        <v>3.12</v>
+        <v>2.87</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.63</v>
+        <v>2.09</v>
       </c>
       <c r="R28" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U28" t="n">
         <v>2.2</v>
       </c>
-      <c r="S28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.73</v>
-      </c>
       <c r="V28" t="n">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.49</v>
+        <v>2.15</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="O31" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="P31" t="n">
-        <v>4.63</v>
+        <v>1.91</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.09</v>
+        <v>3.9</v>
       </c>
       <c r="R31" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="S31" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T31" t="n">
-        <v>3.48</v>
+        <v>2.85</v>
       </c>
       <c r="U31" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="V31" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="W31" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X31" t="n">
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.1</v>
       </c>
-      <c r="Z31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AF31" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.15</v>
+        <v>1.25</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,19 +5495,19 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.9</v>
+        <v>2.63</v>
       </c>
       <c r="R32" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S32" t="n">
         <v>1.36</v>
@@ -5516,37 +5516,37 @@
         <v>2.85</v>
       </c>
       <c r="U32" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="V32" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W32" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
         <v>1.25</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA32" t="n">
         <v>1.85</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF32" t="n">
         <v>1.7</v>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.65</v>
+        <v>1.79</v>
       </c>
       <c r="O36" t="n">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="P36" t="n">
-        <v>2.41</v>
+        <v>3.65</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="O37" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="P37" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="O47" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>6</v>
+        <v>2.05</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="O49" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="P49" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,64 +8357,64 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8720,10 +8720,10 @@
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.09</v>
+        <v>2.43</v>
       </c>
       <c r="O54" t="n">
-        <v>3.4</v>
+        <v>3.57</v>
       </c>
       <c r="P54" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.43</v>
+        <v>2.09</v>
       </c>
       <c r="O55" t="n">
-        <v>3.57</v>
+        <v>3.4</v>
       </c>
       <c r="P55" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,64 +9311,64 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9625,17 +9625,17 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.1</v>
+        <v>2.48</v>
       </c>
       <c r="O62" t="n">
-        <v>7.8</v>
+        <v>2.69</v>
       </c>
       <c r="P62" t="n">
-        <v>16</v>
+        <v>3.09</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10298,10 +10298,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>6.34</v>
+        <v>1.1</v>
       </c>
       <c r="O63" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="P63" t="n">
-        <v>1.39</v>
+        <v>16</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>6.55</v>
+        <v>6.34</v>
       </c>
       <c r="O64" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="P64" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2.48</v>
+        <v>6.55</v>
       </c>
       <c r="O65" t="n">
-        <v>2.69</v>
+        <v>4.5</v>
       </c>
       <c r="P65" t="n">
-        <v>3.09</v>
+        <v>1.4</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10775,10 +10775,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -11336,22 +11336,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11654,22 +11654,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11735,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="O73" t="n">
-        <v>3.06</v>
+        <v>3.44</v>
       </c>
       <c r="P73" t="n">
-        <v>3.2</v>
+        <v>4.38</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -12131,22 +12131,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="O74" t="n">
-        <v>3.41</v>
+        <v>3.1</v>
       </c>
       <c r="P74" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12371,10 +12371,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -12449,22 +12449,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13445,13 +13445,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="O82" t="n">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="P82" t="n">
-        <v>3.31</v>
+        <v>3.69</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="O83" t="n">
-        <v>3.54</v>
+        <v>3.33</v>
       </c>
       <c r="P83" t="n">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13802,10 +13802,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -13961,10 +13961,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14438,10 +14438,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14597,10 +14597,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,49 +14876,49 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>4.05</v>
+        <v>2.12</v>
       </c>
       <c r="O91" t="n">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="P91" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" t="n">
+        <v>0</v>
+      </c>
+      <c r="W91" t="n">
+        <v>0</v>
+      </c>
+      <c r="X91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB91" t="n">
         <v>1.72</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" t="n">
-        <v>0</v>
-      </c>
-      <c r="S91" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" t="n">
-        <v>0</v>
-      </c>
-      <c r="W91" t="n">
-        <v>0</v>
-      </c>
-      <c r="X91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB91" t="n">
-        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="O95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P95" t="n">
-        <v>5.63</v>
+        <v>3.8</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="O96" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P96" t="n">
-        <v>3.9</v>
+        <v>2.55</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15710,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,10 +15869,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="O98" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P98" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16784,13 +16784,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
@@ -16823,10 +16823,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2.01</v>
+        <v>2.5</v>
       </c>
       <c r="O104" t="n">
-        <v>2.99</v>
+        <v>3.45</v>
       </c>
       <c r="P104" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -16982,10 +16982,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -17420,13 +17420,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -17459,10 +17459,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -18056,13 +18056,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O111" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P111" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
@@ -18095,10 +18095,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -18183,12 +18183,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -18215,13 +18215,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O112" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="P112" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
@@ -18254,10 +18254,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.02</v>
+        <v>1.84</v>
       </c>
       <c r="O6" t="n">
-        <v>3.07</v>
+        <v>3.36</v>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>3.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.84</v>
+        <v>3.31</v>
       </c>
       <c r="O8" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>3.87</v>
+        <v>1.76</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>2.63</v>
       </c>
       <c r="R12" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T12" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="U12" t="n">
-        <v>2.9</v>
+        <v>2.39</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.03</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK12" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.63</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S13" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T13" t="n">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.3</v>
+        <v>3.51</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.62</v>
+        <v>1.17</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,58 +3269,58 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="O18" t="n">
         <v>3.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.33</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF18" t="n">
         <v>1.62</v>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,65 +3587,65 @@
         </is>
       </c>
       <c r="N20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG20" t="n">
         <v>2.25</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="O24" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.87</v>
+        <v>1.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.53</v>
+        <v>6.09</v>
       </c>
       <c r="R24" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="S24" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T24" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="U24" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V24" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.85</v>
+        <v>4.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.43</v>
+        <v>1.68</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.59</v>
+        <v>2.04</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.63</v>
+        <v>1.06</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,19 +5336,19 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.9</v>
+        <v>2.63</v>
       </c>
       <c r="R31" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S31" t="n">
         <v>1.36</v>
@@ -5357,37 +5357,37 @@
         <v>2.85</v>
       </c>
       <c r="U31" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="V31" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W31" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
         <v>1.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA31" t="n">
         <v>1.85</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF31" t="n">
         <v>1.7</v>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,19 +5495,19 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.63</v>
+        <v>3.9</v>
       </c>
       <c r="R32" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S32" t="n">
         <v>1.36</v>
@@ -5516,37 +5516,37 @@
         <v>2.85</v>
       </c>
       <c r="U32" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="V32" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W32" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
         <v>1.25</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA32" t="n">
         <v>1.85</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF32" t="n">
         <v>1.7</v>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.78</v>
+        <v>2.53</v>
       </c>
       <c r="O37" t="n">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="P37" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R37" t="n">
         <v>2.3</v>
       </c>
       <c r="S37" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="T37" t="n">
-        <v>3.34</v>
+        <v>2.73</v>
       </c>
       <c r="U37" t="n">
-        <v>2.36</v>
+        <v>2.87</v>
       </c>
       <c r="V37" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="W37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE37" t="n">
         <v>1.1</v>
       </c>
-      <c r="X37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF37" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.12</v>
+        <v>2.78</v>
       </c>
       <c r="O40" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P40" t="n">
-        <v>2.48</v>
+        <v>2.05</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.53</v>
+        <v>2.12</v>
       </c>
       <c r="O41" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="P41" t="n">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="O44" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="P44" t="n">
-        <v>8.550000000000001</v>
+        <v>6</v>
       </c>
       <c r="Q44" t="n">
-        <v>6.75</v>
+        <v>1.71</v>
       </c>
       <c r="R44" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="S44" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T44" t="n">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="U44" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="V44" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="W44" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z44" t="n">
-        <v>5.8</v>
+        <v>5.35</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>3.3</v>
+        <v>1.09</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.02</v>
+        <v>3.08</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="O45" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="P45" t="n">
-        <v>4.3</v>
+        <v>4.08</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="R45" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="S45" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T45" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U45" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="V45" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="W45" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X45" t="n">
         <v>1.03</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z45" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE45" t="n">
         <v>1.22</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK45" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="P47" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X48" t="n">
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.82</v>
+        <v>1.53</v>
       </c>
       <c r="O49" t="n">
-        <v>3.88</v>
+        <v>4.2</v>
       </c>
       <c r="P49" t="n">
-        <v>2.11</v>
+        <v>4.3</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.1</v>
+        <v>2.07</v>
       </c>
       <c r="R49" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="S49" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="T49" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="U49" t="n">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
       <c r="V49" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="W49" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X49" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z49" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.4</v>
+        <v>2.21</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,64 +8357,64 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="O54" t="n">
-        <v>3.57</v>
+        <v>3.43</v>
       </c>
       <c r="P54" t="n">
-        <v>2.85</v>
+        <v>3.07</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,64 +9152,64 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.09</v>
+        <v>2.37</v>
       </c>
       <c r="O55" t="n">
         <v>3.4</v>
       </c>
       <c r="P55" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AB55" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,64 +9311,64 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="AJ56" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9625,68 +9625,68 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK58" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL58" t="n">
         <v>0</v>
@@ -9788,64 +9788,64 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O59" t="n">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="P59" t="n">
-        <v>3.37</v>
+        <v>2.96</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="AJ59" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK59" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL59" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.48</v>
+        <v>1.1</v>
       </c>
       <c r="O62" t="n">
-        <v>2.69</v>
+        <v>7.8</v>
       </c>
       <c r="P62" t="n">
-        <v>3.09</v>
+        <v>16</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10298,10 +10298,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.1</v>
+        <v>2.48</v>
       </c>
       <c r="O63" t="n">
-        <v>7.8</v>
+        <v>2.69</v>
       </c>
       <c r="P63" t="n">
-        <v>16</v>
+        <v>3.09</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10457,10 +10457,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.24</v>
+        <v>3.09</v>
       </c>
       <c r="O66" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="P66" t="n">
-        <v>3.61</v>
+        <v>2.44</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10934,10 +10934,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>3.09</v>
+        <v>2.24</v>
       </c>
       <c r="O67" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="P67" t="n">
-        <v>2.44</v>
+        <v>3.61</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11093,10 +11093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -11336,22 +11336,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="O70" t="n">
-        <v>3.22</v>
+        <v>3.06</v>
       </c>
       <c r="P70" t="n">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11576,10 +11576,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2.3</v>
+        <v>1.31</v>
       </c>
       <c r="O71" t="n">
-        <v>3.06</v>
+        <v>5.34</v>
       </c>
       <c r="P71" t="n">
-        <v>3.2</v>
+        <v>10.7</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11735,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11894,10 +11894,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -11972,22 +11972,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,64 +12014,64 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1.92</v>
+        <v>2.29</v>
       </c>
       <c r="O73" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="P73" t="n">
-        <v>4.38</v>
+        <v>3.2</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12084,10 +12084,10 @@
         </is>
       </c>
       <c r="AJ73" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK73" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL73" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="O74" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="P74" t="n">
-        <v>3.15</v>
+        <v>3.43</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12449,22 +12449,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12608,22 +12608,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="O79" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P79" t="n">
-        <v>3.7</v>
+        <v>2.84</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13007,10 +13007,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="O80" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P80" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13166,10 +13166,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="O81" t="n">
         <v>2.9</v>
       </c>
       <c r="P81" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13445,13 +13445,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="O82" t="n">
-        <v>3.54</v>
+        <v>3.33</v>
       </c>
       <c r="P82" t="n">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="O83" t="n">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="P83" t="n">
-        <v>3.31</v>
+        <v>3.69</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13802,10 +13802,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14438,10 +14438,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14597,10 +14597,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2.12</v>
+        <v>4.05</v>
       </c>
       <c r="O91" t="n">
-        <v>3.3</v>
+        <v>3.66</v>
       </c>
       <c r="P91" t="n">
-        <v>3.32</v>
+        <v>1.72</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14915,10 +14915,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,49 +15035,49 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>4.05</v>
+        <v>2.12</v>
       </c>
       <c r="O92" t="n">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="P92" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" t="n">
+        <v>0</v>
+      </c>
+      <c r="W92" t="n">
+        <v>0</v>
+      </c>
+      <c r="X92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB92" t="n">
         <v>1.72</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" t="n">
-        <v>0</v>
-      </c>
-      <c r="V92" t="n">
-        <v>0</v>
-      </c>
-      <c r="W92" t="n">
-        <v>0</v>
-      </c>
-      <c r="X92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB92" t="n">
-        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="O94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P94" t="n">
-        <v>5.63</v>
+        <v>3.8</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1.95</v>
+        <v>1.51</v>
       </c>
       <c r="O95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P95" t="n">
-        <v>3.8</v>
+        <v>5.63</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>2.5</v>
+        <v>1.61</v>
       </c>
       <c r="O96" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P96" t="n">
-        <v>2.55</v>
+        <v>4.4</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15710,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="O98" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P98" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2.01</v>
+        <v>2.5</v>
       </c>
       <c r="O99" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P99" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="O100" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P100" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16664,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -16982,10 +16982,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G107" t="n">

--- a/jogos_2026-05-30.xlsx
+++ b/jogos_2026-05-30.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.02</v>
+        <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>3.07</v>
+        <v>3.36</v>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>3.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.31</v>
+        <v>3.02</v>
       </c>
       <c r="O8" t="n">
-        <v>3.25</v>
+        <v>3.07</v>
       </c>
       <c r="P8" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.63</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S12" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="U12" t="n">
-        <v>2.39</v>
+        <v>2.9</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.08</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>2.63</v>
       </c>
       <c r="R13" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="U13" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.17</v>
+        <v>1.62</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.06</v>
+        <v>2.78</v>
       </c>
       <c r="O15" t="n">
-        <v>3.18</v>
+        <v>3.61</v>
       </c>
       <c r="P15" t="n">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="Q15" t="n">
         <v>2.63</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T15" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="U15" t="n">
-        <v>2.78</v>
+        <v>2.39</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.03</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.3</v>
+        <v>4.16</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>1.3</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.53</v>
+        <v>2.78</v>
       </c>
       <c r="O37" t="n">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="P37" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
         <v>2.3</v>
       </c>
       <c r="S37" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="T37" t="n">
-        <v>2.73</v>
+        <v>3.34</v>
       </c>
       <c r="U37" t="n">
-        <v>2.87</v>
+        <v>2.36</v>
       </c>
       <c r="V37" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="W37" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X37" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0